--- a/product_selector_out/STM32L0x1.xlsx
+++ b/product_selector_out/STM32L0x1.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -85,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -99,6 +104,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -18531,9 +18537,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX12" s="7" t="inlineStr">
@@ -18858,9 +18864,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX13" s="7" t="inlineStr">
@@ -19185,9 +19191,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX14" s="7" t="inlineStr">
@@ -19512,9 +19518,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX15" s="7" t="inlineStr">
@@ -19839,9 +19845,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX16" s="7" t="inlineStr">
@@ -20166,9 +20172,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX17" s="7" t="inlineStr">
@@ -20493,9 +20499,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX18" s="7" t="inlineStr">
@@ -20820,9 +20826,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX19" s="7" t="inlineStr">
@@ -21147,9 +21153,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX20" s="7" t="inlineStr">
@@ -21474,9 +21480,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX21" s="7" t="inlineStr">
@@ -21801,9 +21807,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX22" s="7" t="inlineStr">
@@ -22128,9 +22134,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX23" s="7" t="inlineStr">
@@ -22455,9 +22461,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX24" s="7" t="inlineStr">
@@ -22782,9 +22788,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX25" s="7" t="inlineStr">
@@ -23109,9 +23115,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX26" s="7" t="inlineStr">
@@ -23436,9 +23442,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX27" s="7" t="inlineStr">
@@ -23763,9 +23769,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX28" s="7" t="inlineStr">
@@ -24090,9 +24096,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX29" s="7" t="inlineStr">
@@ -24417,9 +24423,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX30" s="7" t="inlineStr">
@@ -24744,9 +24750,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX31" s="7" t="inlineStr">
@@ -25071,9 +25077,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX32" s="7" t="inlineStr">
@@ -25398,9 +25404,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX33" s="7" t="inlineStr">
@@ -25725,9 +25731,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX34" s="7" t="inlineStr">
@@ -26052,9 +26058,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX35" s="7" t="inlineStr">
@@ -26379,9 +26385,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX36" s="7" t="inlineStr">
@@ -26706,9 +26712,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX37" s="7" t="inlineStr">
@@ -27033,9 +27039,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW38" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX38" s="7" t="inlineStr">
@@ -27360,9 +27366,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX39" s="7" t="inlineStr">
@@ -27687,9 +27693,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX40" s="7" t="inlineStr">
@@ -28014,9 +28020,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW41" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX41" s="7" t="inlineStr">
@@ -28341,9 +28347,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX42" s="7" t="inlineStr">
@@ -28668,9 +28674,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX43" s="7" t="inlineStr">
@@ -28995,9 +29001,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX44" s="7" t="inlineStr">
@@ -29322,9 +29328,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW45" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX45" s="7" t="inlineStr">
@@ -29649,9 +29655,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX46" s="7" t="inlineStr">
@@ -29976,9 +29982,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW47" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX47" s="7" t="inlineStr">
@@ -30303,9 +30309,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW48" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW48" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX48" s="7" t="inlineStr">
@@ -30630,9 +30636,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW49" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW49" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX49" s="7" t="inlineStr">
@@ -30957,9 +30963,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW50" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW50" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX50" s="7" t="inlineStr">
@@ -31284,9 +31290,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW51" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW51" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX51" s="7" t="inlineStr">
@@ -31611,9 +31617,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW52" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW52" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX52" s="7" t="inlineStr">
@@ -31938,9 +31944,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW53" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW53" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX53" s="7" t="inlineStr">
@@ -32265,9 +32271,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX54" s="7" t="inlineStr">
@@ -32592,9 +32598,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW55" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW55" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX55" s="7" t="inlineStr">
@@ -32919,9 +32925,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW56" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX56" s="7" t="inlineStr">
@@ -33246,9 +33252,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW57" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW57" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX57" s="7" t="inlineStr">
@@ -33573,9 +33579,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW58" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW58" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX58" s="7" t="inlineStr">
@@ -33900,9 +33906,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW59" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW59" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX59" s="7" t="inlineStr">
@@ -34227,9 +34233,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW60" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW60" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX60" s="7" t="inlineStr">
@@ -34554,9 +34560,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX61" s="7" t="inlineStr">
@@ -34881,9 +34887,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW62" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX62" s="7" t="inlineStr">
@@ -34982,7 +34988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -35013,7 +35019,1128 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STM32L011F4</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STM32L071KB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STM32L011K3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32L081KZ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32L071KZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32L071CZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32L011D4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32L011K4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32L071RZ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32L041E6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32L071VZ</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32L011G3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32L021G4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32L031F4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32L051T6</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32L021F4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32L051T8</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32L011E3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32L011F3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32L031G4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32L041K6</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32L031K4</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32L071VB</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32L041C6</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32L081CZ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32L041F6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32L011E4</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM32L021K4</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STM32L031E6</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM32L011D3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STM32L031G6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STM32L021D4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM32L031F6</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM32L031C4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32L031K6</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32L071V8</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STM32L051K6</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STM32L031E4</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32L041G6</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STM32L071K8</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>STM32L071C8</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>STM32L071CB</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>STM32L011G4</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Table 18. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STM32L031C6</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>STM32L071RB</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Table 25. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STM32L081CB</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Table 20. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STM32L051C8</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STM32L051R6</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>STM32L051K8</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>STM32L051C6</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>STM32L051R8</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32L0x1.xlsx
+++ b/product_selector_out/STM32L0x1.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM62"/>
+  <dimension ref="A1:BN62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.40625" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l081cb.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l041c6.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l021d4.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l021d4.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -7854,6 +7961,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l041c6.pdf</t>
         </is>
       </c>
@@ -8181,6 +8293,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -8508,6 +8625,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -8835,6 +8957,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l041c6.pdf</t>
         </is>
       </c>
@@ -9162,6 +9289,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l081cb.pdf</t>
         </is>
       </c>
@@ -9489,6 +9621,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l041c6.pdf</t>
         </is>
       </c>
@@ -9816,6 +9953,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -10143,6 +10285,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l021d4.pdf</t>
         </is>
       </c>
@@ -10470,6 +10617,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -10797,6 +10949,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -11124,6 +11281,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -11451,6 +11613,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l021d4.pdf</t>
         </is>
       </c>
@@ -11778,6 +11945,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -12105,6 +12277,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -12432,6 +12609,11 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -12759,6 +12941,11 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -13086,6 +13273,11 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
@@ -13413,6 +13605,11 @@
       </c>
       <c r="BM49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -13740,6 +13937,11 @@
       </c>
       <c r="BM50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l041c6.pdf</t>
         </is>
       </c>
@@ -14067,6 +14269,11 @@
       </c>
       <c r="BM51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -14394,6 +14601,11 @@
       </c>
       <c r="BM52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -14721,6 +14933,11 @@
       </c>
       <c r="BM53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -15048,6 +15265,11 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l011d3.pdf</t>
         </is>
       </c>
@@ -15375,6 +15597,11 @@
       </c>
       <c r="BM55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l031c4.pdf</t>
         </is>
       </c>
@@ -15702,6 +15929,11 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l071c8.pdf</t>
         </is>
       </c>
@@ -16029,6 +16261,11 @@
       </c>
       <c r="BM57" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l081cb.pdf</t>
         </is>
       </c>
@@ -16356,6 +16593,11 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
@@ -16683,6 +16925,11 @@
       </c>
       <c r="BM59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
@@ -17010,6 +17257,11 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
@@ -17337,6 +17589,11 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
@@ -17664,12 +17921,17 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l051c6.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -17690,16 +17952,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -17712,6 +17972,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -17731,7 +17992,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -17799,7 +18062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM62"/>
+  <dimension ref="A1:BN62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17867,6 +18130,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18200,6 +18464,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -18295,6 +18564,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -18617,7 +18887,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18944,7 +19219,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19271,7 +19551,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19598,7 +19883,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19925,7 +20215,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20252,7 +20547,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20579,7 +20879,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20906,7 +21211,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21233,7 +21543,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21560,7 +21875,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21887,7 +22207,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22214,7 +22539,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22541,7 +22871,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22868,7 +23203,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23195,7 +23535,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23522,7 +23867,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23849,7 +24199,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24176,7 +24531,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24503,7 +24863,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24830,7 +25195,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25157,7 +25527,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25484,7 +25859,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25811,7 +26191,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26138,7 +26523,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26465,7 +26855,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26792,7 +27187,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27119,7 +27519,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27446,7 +27851,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27773,7 +28183,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28100,7 +28515,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28427,7 +28847,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28754,7 +29179,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29081,7 +29511,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29408,7 +29843,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29735,7 +30175,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30062,7 +30507,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
+      <c r="BM47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30389,7 +30839,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
+      <c r="BM48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30716,7 +31171,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM49" s="6" t="inlineStr">
+      <c r="BM49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31043,7 +31503,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM50" s="6" t="inlineStr">
+      <c r="BM50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31370,7 +31835,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM51" s="6" t="inlineStr">
+      <c r="BM51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31697,7 +32167,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM52" s="6" t="inlineStr">
+      <c r="BM52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32024,7 +32499,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM53" s="6" t="inlineStr">
+      <c r="BM53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32351,7 +32831,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
+      <c r="BM54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32678,7 +33163,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM55" s="6" t="inlineStr">
+      <c r="BM55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33005,7 +33495,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
+      <c r="BM56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33332,7 +33827,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM57" s="6" t="inlineStr">
+      <c r="BM57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33659,7 +34159,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="6" t="inlineStr">
+      <c r="BM58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33986,7 +34491,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM59" s="6" t="inlineStr">
+      <c r="BM59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34313,7 +34823,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
+      <c r="BM60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34640,7 +35155,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
+      <c r="BM61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34967,7 +35487,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="6" t="inlineStr">
+      <c r="BM62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34975,8 +35500,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
